--- a/Result/profitability/6235.xlsx
+++ b/Result/profitability/6235.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.41</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4712500000000001</v>
+        <v>0.4025</v>
       </c>
       <c r="N2" t="n">
-        <v>24.6275</v>
+        <v>24.09625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.64</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3100000000000001</v>
+        <v>0.28125</v>
       </c>
       <c r="N3" t="n">
-        <v>20.0775</v>
+        <v>20.09625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.27</v>
       </c>
       <c r="M4" t="n">
-        <v>0.235</v>
+        <v>0.17</v>
       </c>
       <c r="N4" t="n">
-        <v>17.84875</v>
+        <v>17.75125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-5.84</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5725</v>
+        <v>-0.69375</v>
       </c>
       <c r="N5" t="n">
-        <v>13.01875</v>
+        <v>12.69625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.97</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8275</v>
+        <v>-0.8975</v>
       </c>
       <c r="N6" t="n">
-        <v>9.93</v>
+        <v>9.827500000000001</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-1.24</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.065</v>
+        <v>-1.12125</v>
       </c>
       <c r="N7" t="n">
-        <v>2.742500000000001</v>
+        <v>2.52875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-1.2</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.28375</v>
+        <v>-1.30875</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.76125</v>
+        <v>-2.7325</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1521,7 +1521,7 @@
         <v>-1.41875</v>
       </c>
       <c r="N9" t="n">
-        <v>-9.376249999999999</v>
+        <v>-9.376250000000001</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
         <v>-0.60875</v>
       </c>
       <c r="N13" t="n">
-        <v>-6.86</v>
+        <v>-6.859999999999999</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6235</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1590</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1198</v>
+      </c>
+      <c r="E75" t="n">
+        <v>392</v>
+      </c>
+      <c r="F75" t="n">
+        <v>24.66</v>
+      </c>
+      <c r="G75" t="n">
+        <v>81</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>5.06%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-36</v>
+      </c>
+      <c r="J75" t="n">
+        <v>45</v>
+      </c>
+      <c r="K75" t="n">
+        <v>20</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="N75" t="n">
+        <v>25.88</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.2300000000000004</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.009414654113794496</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.9700000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.9065420560747663</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-2.579999999999998</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.09471365638766516</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
